--- a/public/templates/office/EMP_TST_030_보안점검결과서.xlsx
+++ b/public/templates/office/EMP_TST_030_보안점검결과서.xlsx
@@ -543,7 +543,7 @@
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>아모레퍼시픽 AI 기반 화장품 표시광고 심의 및 리스크 예방 시스템 구축</t>
+          <t>한빛글로벌 엔터프라이즈 AI 콘텐츠·규제 심의 자동화 시스템(SyncGuard AI) 구축</t>
         </is>
       </c>
     </row>
@@ -591,7 +591,7 @@
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>(주)아모레퍼시픽 (HANBIT GLOBAL)</t>
+          <t>㈜한빛글로벌 (Hanbit Global Corp.)</t>
         </is>
       </c>
     </row>
@@ -603,7 +603,7 @@
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>㈜그로브소프트 (EMPASY)</t>
+          <t>㈜엠파시 (Empasy Inc.)</t>
         </is>
       </c>
     </row>
@@ -615,7 +615,7 @@
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>아모레퍼시픽 정보보안센터 / 한국인터넷진흥원(KISA) 기준</t>
+          <t>한빛글로벌 정보보안센터 / 한국인터넷진흥원(KISA) 기준</t>
         </is>
       </c>
     </row>
@@ -1210,7 +1210,7 @@
       </c>
       <c r="G18" s="4" t="inlineStr">
         <is>
-          <t>허용된 아모레퍼시픽 사내 도메인만 Access-Control-Allow-Origin 허용</t>
+          <t>허용된 한빛글로벌 사내 도메인만 Access-Control-Allow-Origin 허용</t>
         </is>
       </c>
       <c r="H18" s="10" t="inlineStr">

--- a/public/templates/office/EMP_TST_030_보안점검결과서.xlsx
+++ b/public/templates/office/EMP_TST_030_보안점검결과서.xlsx
@@ -530,7 +530,7 @@
     <row r="3">
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>SyncGuard AI 시스템 웹 애플리케이션 취약점, 시큐어 코딩 및 인프라 보안 진단 결과서</t>
+          <t>SyncFlow AI 시스템 웹 애플리케이션 취약점, 시큐어 코딩 및 인프라 보안 진단 결과서</t>
         </is>
       </c>
     </row>
@@ -543,7 +543,7 @@
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>한빛글로벌 엔터프라이즈 AI 콘텐츠·규제 심의 자동화 시스템(SyncGuard AI) 구축</t>
+          <t>한빛글로벌 지능형 공급망 구매·조달 계약 및 부품 품질규격 AI 검증 플랫폼(SyncFlow AI) 구축</t>
         </is>
       </c>
     </row>
@@ -803,7 +803,7 @@
       </c>
       <c r="G7" s="8" t="inlineStr">
         <is>
-          <t>시안 업로드 파일명 UUID 난수화 및 상대경로(../) 전면 차단</t>
+          <t>계약·도서 업로드 파일명 UUID 난수화 및 상대경로(../) 전면 차단</t>
         </is>
       </c>
       <c r="H7" s="7" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="G14" s="4" t="inlineStr">
         <is>
-          <t>Spring Security RBAC Role-based URL 인터셉터 적용 (/claim/admin/* 차단)</t>
+          <t>Spring Security RBAC Role-based URL 인터셉터 적용 (/Spec/admin/* 차단)</t>
         </is>
       </c>
       <c r="H14" s="10" t="inlineStr">
@@ -1121,7 +1121,7 @@
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>시안 이미지 불법 접근</t>
+          <t>계약·도서 이미지 불법 접근</t>
         </is>
       </c>
       <c r="E16" s="10" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="G19" s="8" t="inlineStr">
         <is>
-          <t>임상시험 피험자 성명/주민번호 마스킹 및 비식별화 처리</t>
+          <t>신뢰성시험 시험시료 성명/주민번호 마스킹 및 비식별화 처리</t>
         </is>
       </c>
       <c r="H19" s="7" t="inlineStr">
@@ -1321,7 +1321,7 @@
       </c>
       <c r="G21" s="8" t="inlineStr">
         <is>
-          <t>시안 텍스트 내 시스템 프롬프트 탈취 악의적 지시어 사전 차단 필터 적용</t>
+          <t>계약·도서 텍스트 내 시스템 프롬프트 탈취 악의적 지시어 사전 차단 필터 적용</t>
         </is>
       </c>
       <c r="H21" s="7" t="inlineStr">
@@ -1358,7 +1358,7 @@
       </c>
       <c r="G22" s="4" t="inlineStr">
         <is>
-          <t>Docker non-root 전용 사용자(syncguardapp)로 프로세스 격리 실행</t>
+          <t>Docker non-root 전용 사용자(syncflowapp)로 프로세스 격리 실행</t>
         </is>
       </c>
       <c r="H22" s="10" t="inlineStr">
